--- a/data/wordwise_global_visualization.xlsx
+++ b/data/wordwise_global_visualization.xlsx
@@ -589,12 +589,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>06.01.2025</t>
+          <t>6/1/2025</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>01-04-2025</t>
+          <t>January 4, 2025</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>01-18-2025</t>
+          <t>18-Jan-2025</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Solara shop</t>
+          <t xml:space="preserve">Solara shop </t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>23.02.2025</t>
+          <t>Feb 23, 2025</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
@@ -891,12 +891,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>05-16-2025</t>
+          <t>16/5/2025</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>05-26-2025</t>
+          <t>May 26, 2025</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t xml:space="preserve">DRAFT </t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>15-Jan-2025</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>01-20-2025</t>
+          <t>Jan 20, 2025</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>22.01.2025</t>
+          <t>22/1/2025</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>05-28-2025</t>
+          <t>May 28, 2025</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>06-23-2025</t>
+          <t>23-Jun-2025</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>05-05-2025</t>
+          <t>May 5, 2025</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>14.05.2025</t>
+          <t>14/5/2025</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>06-26-2025</t>
+          <t>June 26, 2025</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>04-11-2025</t>
+          <t>11-Apr-2025</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>Apr 17, 2025</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>03-06-2025</t>
+          <t>6/3/2025</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>April 28, 2025</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>16.06.2025</t>
+          <t>16-Jun-2025</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>06-06-2025</t>
+          <t>Jun 6, 2025</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>04.02.2025</t>
+          <t>4/2/2025</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>February 4, 2025</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>04.02.2025</t>
+          <t>4-Feb-2025</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>Feb 4, 2025</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>02-28-2025</t>
+          <t>28/2/2025</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>02-28-2025</t>
+          <t>February 28, 2025</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>25.04.2025</t>
+          <t>25-Apr-2025</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>25.04.2025</t>
+          <t>Apr 25, 2025</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>28/2/2025</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>06-04-2025</t>
+          <t>June 4, 2025</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>01-13-2025</t>
+          <t>13-Jan-2025</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>01-12-2025</t>
+          <t>Jan 12, 2025</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>28.05.2025</t>
+          <t>28/5/2025</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>04-12-2025</t>
+          <t>April 12, 2025</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>06-16-2025</t>
+          <t>16-Jun-2025</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>22.06.2025</t>
+          <t>Jun 22, 2025</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>03-26-2025</t>
+          <t>26/3/2025</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>21.03.2025</t>
+          <t>March 21, 2025</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>26-Mar-2025</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>Mar 28, 2025</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>05-09-2025</t>
+          <t>9/5/2025</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>05-13-2025</t>
+          <t>May 13, 2025</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>05-13-2025</t>
+          <t>13-May-2025</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>14.05.2025</t>
+          <t>May 14, 2025</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>06-14-2025</t>
+          <t>14/6/2025</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>01-21-2025</t>
+          <t>January 21, 2025</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>5-Jun-2025</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>Jun 6, 2025</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>02-02-2025</t>
+          <t>2/2/2025</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>05.02.2025</t>
+          <t>February 5, 2025</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>07.05.2025</t>
+          <t>7-May-2025</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>Apr 22, 2025</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>10.04.2025</t>
+          <t>10/4/2025</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>10.04.2025</t>
+          <t>April 10, 2025</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>04-10-2025</t>
+          <t>10-Apr-2025</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>20.04.2025</t>
+          <t>Apr 20, 2025</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>04-11-2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>03-28-2025</t>
+          <t>March 28, 2025</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>25.01.2025</t>
+          <t>25-Jan-2025</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>25.01.2025</t>
+          <t>Jan 25, 2025</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>23.02.2025</t>
+          <t>23/2/2025</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>June 26, 2025</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>04.06.2025</t>
+          <t>4-Jun-2025</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">

--- a/data/wordwise_global_visualization.xlsx
+++ b/data/wordwise_global_visualization.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>January 4, 2025</t>
+          <t>4-Jan-2025</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>18/01/2025</t>
+          <t>18 Jan 2025</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>18-Jan-2025</t>
+          <t>18.1.2025</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>March 10, 2025</t>
+          <t>10-3-2025</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>10 Mar 2025</t>
+          <t>10 Mar, 2025</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>February 25, 2025</t>
+          <t>25/2/2025</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Feb 23, 2025</t>
+          <t>23-Feb-2025</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
@@ -829,12 +829,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>7 Mar 2025</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>9 Mar 2025</t>
+          <t>9.3.2025</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>16/5/2025</t>
+          <t>16-5-2025</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>May 26, 2025</t>
+          <t>26 May, 2025</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2 May 2025</t>
+          <t>2/5/2025</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>5-May-2025</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>15-Jan-2025</t>
+          <t>15 Jan 2025</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>January 19, 2025</t>
+          <t>19.1.2025</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Jan 20, 2025</t>
+          <t>20-1-2025</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>22/1/2025</t>
+          <t>22 Jan, 2025</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>May 28, 2025</t>
+          <t>28/5/2025</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>May 28, 2025</t>
+          <t>28-May-2025</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>23-Jun-2025</t>
+          <t>23 Jun 2025</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>28 Jun 2025</t>
+          <t>28.6.2025</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>5-5-2025</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>May 9, 2025</t>
+          <t>9 May, 2025</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>5/5/2025</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>14/5/2025</t>
+          <t>14-May-2025</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>June 26, 2025</t>
+          <t>26 Jun 2025</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>25 Jun 2025</t>
+          <t>25.6.2025</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>15/02/2025</t>
+          <t>15-2-2025</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>February 17, 2025</t>
+          <t>17 Feb, 2025</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>4 May 2025</t>
+          <t>4/5/2025</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>5-May-2025</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>11-Apr-2025</t>
+          <t>11 Apr 2025</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Apr 17, 2025</t>
+          <t>17.4.2025</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>6/3/2025</t>
+          <t>6-3-2025</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>15 Mar, 2025</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>April 23, 2025</t>
+          <t>23/4/2025</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>April 28, 2025</t>
+          <t>28-Apr-2025</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>22/06/2025</t>
+          <t>22 Jun 2025</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>June 23, 2025</t>
+          <t>23.6.2025</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>19 Jun 2025</t>
+          <t>19-6-2025</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>16-Jun-2025</t>
+          <t>16 Jun, 2025</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Jun 6, 2025</t>
+          <t>6/6/2025</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>15/06/2025</t>
+          <t>15-Jun-2025</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>4/2/2025</t>
+          <t>4 Feb 2025</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>February 4, 2025</t>
+          <t>4.2.2025</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>4-Feb-2025</t>
+          <t>4-2-2025</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Feb 4, 2025</t>
+          <t>4 Feb, 2025</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>27/2/2025</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>28/2/2025</t>
+          <t>28-Feb-2025</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>27 Feb 2025</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>February 28, 2025</t>
+          <t>28.2.2025</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>25-Apr-2025</t>
+          <t>25-4-2025</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>28 Apr 2025</t>
+          <t>28 Apr, 2025</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Apr 25, 2025</t>
+          <t>25/4/2025</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>28 Apr 2025</t>
+          <t>28-Apr-2025</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>28/2/2025</t>
+          <t>28.2.2025</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>June 4, 2025</t>
+          <t>4-6-2025</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>04/06/2025</t>
+          <t>4 Jun, 2025</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>June 10, 2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>June 15, 2025</t>
+          <t>15-Jun-2025</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>13-Jan-2025</t>
+          <t>13 Jan 2025</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>17/01/2025</t>
+          <t>17.1.2025</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>25-6-2025</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>25 Jun, 2025</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>6 Jan 2025</t>
+          <t>6/1/2025</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>9 Jan 2025</t>
+          <t>9-Jan-2025</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Jan 12, 2025</t>
+          <t>12.1.2025</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>28/5/2025</t>
+          <t>28-5-2025</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>April 12, 2025</t>
+          <t>12 Apr, 2025</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>April 14, 2025</t>
+          <t>14/4/2025</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Jun 22, 2025</t>
+          <t>22 Jun 2025</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/01/2025</t>
+          <t>27.1.2025</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>28 Jan 2025</t>
+          <t>28-1-2025</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>March 17, 2025</t>
+          <t>17 Mar, 2025</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>March 21, 2025</t>
+          <t>21-Mar-2025</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>26-Mar-2025</t>
+          <t>26 Mar 2025</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>22/03/2025</t>
+          <t>22.3.2025</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Mar 28, 2025</t>
+          <t>28-3-2025</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>April 26, 2025</t>
+          <t>26 Apr, 2025</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>April 23, 2025</t>
+          <t>23/4/2025</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>9/5/2025</t>
+          <t>9-May-2025</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>May 13, 2025</t>
+          <t>13 May 2025</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>June 4, 2025</t>
+          <t>4.6.2025</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>June 6, 2025</t>
+          <t>6-6-2025</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>13-May-2025</t>
+          <t>13 May, 2025</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>May 14, 2025</t>
+          <t>14/5/2025</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>14/6/2025</t>
+          <t>14-Jun-2025</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>June 23, 2025</t>
+          <t>23 Jun 2025</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>January 21, 2025</t>
+          <t>21.1.2025</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>January 28, 2025</t>
+          <t>28-1-2025</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>5-Jun-2025</t>
+          <t>5 Jun, 2025</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Jun 6, 2025</t>
+          <t>6/6/2025</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2/2/2025</t>
+          <t>2-Feb-2025</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>February 5, 2025</t>
+          <t>5 Feb 2025</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>7-May-2025</t>
+          <t>7.5.2025</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Apr 22, 2025</t>
+          <t>22-4-2025</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>April 22, 2025</t>
+          <t>22 Apr, 2025</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr"/>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>13/04/2025</t>
+          <t>13-Apr-2025</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>April 10, 2025</t>
+          <t>10 Apr 2025</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>13/04/2025</t>
+          <t>13.4.2025</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>10-Apr-2025</t>
+          <t>10-4-2025</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>April 11, 2025</t>
+          <t>11 Apr, 2025</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>23/03/2025</t>
+          <t>23/3/2025</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>28 Mar 2025</t>
+          <t>28-Mar-2025</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>22/04/2025</t>
+          <t>22 Apr 2025</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Apr 20, 2025</t>
+          <t>20.4.2025</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11-4-2025</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr"/>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>21 Mar 2025</t>
+          <t>21 Mar, 2025</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>March 28, 2025</t>
+          <t>28/3/2025</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Jan 25, 2025</t>
+          <t>25 Jan 2025</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>22 Feb 2025</t>
+          <t>22.2.2025</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>23/2/2025</t>
+          <t>23-2-2025</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>22 Jun 2025</t>
+          <t>22 Jun, 2025</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>June 26, 2025</t>
+          <t>26/6/2025</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>June 7, 2025</t>
+          <t>7 Jun 2025</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>February 1, 2025</t>
+          <t>1.2.2025</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>01/02/2025</t>
+          <t>1-2-2025</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
